--- a/products_for_the_menu.xlsx
+++ b/products_for_the_menu.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Office30\Documents\ATLAS\Mid Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Office30\Documents\ATLAS\Mid Project\IKAR1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97465A3-550C-4558-818C-6F6623B9DA9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{870079BF-2BF3-41A4-8026-97FD4DEEE806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,32 +33,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="125">
-  <si>
-    <t>Assorted omelets</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="127">
   <si>
     <t>Antipasti</t>
   </si>
   <si>
-    <t>Bruschettas with a variety of toppings</t>
-  </si>
-  <si>
     <t>Mini tortillas</t>
   </si>
   <si>
     <t>category</t>
   </si>
   <si>
-    <t>Assorted quiches</t>
-  </si>
-  <si>
-    <t>Braided challah with cheeses and roasted vegetables</t>
-  </si>
-  <si>
-    <t>Selection of wood-fired oven pizzas</t>
-  </si>
-  <si>
     <t>Fish &amp; Chips</t>
   </si>
   <si>
@@ -86,9 +71,6 @@
     <t>Pizzas</t>
   </si>
   <si>
-    <t>Pasta – Roasted Vegetables, Rosé Sauce, Mushroom &amp; Truffle Cream Sauce</t>
-  </si>
-  <si>
     <t>Farmer's Land Salad</t>
   </si>
   <si>
@@ -104,48 +86,18 @@
     <t>Artichoke Salad</t>
   </si>
   <si>
-    <t>A selection of assorted desserts</t>
-  </si>
-  <si>
     <t>Coffee</t>
   </si>
   <si>
     <t>Orange Juice</t>
   </si>
   <si>
-    <t>lemonade Juice</t>
-  </si>
-  <si>
     <t>addons</t>
   </si>
   <si>
-    <t>Assorted quiches with a variety of flavors</t>
-  </si>
-  <si>
-    <t>Farm cheese platter</t>
-  </si>
-  <si>
-    <t>Pasta with your choice of sauce</t>
-  </si>
-  <si>
-    <t>Spinach or Chestnut Ravioli with your choice of sauce</t>
-  </si>
-  <si>
-    <t>Assorted pizzas</t>
-  </si>
-  <si>
-    <t>Fish meatballs in tomato sauce</t>
-  </si>
-  <si>
-    <t>Oven-baked salmon fillet in marinade</t>
-  </si>
-  <si>
     <t>Burrata Salad</t>
   </si>
   <si>
-    <t>Lemonade Juice</t>
-  </si>
-  <si>
     <t>Lemonade</t>
   </si>
   <si>
@@ -158,9 +110,6 @@
     <t>Home Salad</t>
   </si>
   <si>
-    <t>A selection of assorted Desserts</t>
-  </si>
-  <si>
     <t>addons_price</t>
   </si>
   <si>
@@ -173,27 +122,12 @@
     <t>Alcoholic drink</t>
   </si>
   <si>
-    <t>Alcoholic drink Subject to availability</t>
-  </si>
-  <si>
-    <t>Soda or any other carbonated beverage</t>
-  </si>
-  <si>
-    <t>Free draft beer</t>
-  </si>
-  <si>
     <t>Fruit platters</t>
   </si>
   <si>
-    <t>Seasonal fruit platters</t>
-  </si>
-  <si>
     <t>Extra Desserts</t>
   </si>
   <si>
-    <t>Extra Desserts to the Desserts all ready in the offer</t>
-  </si>
-  <si>
     <t>M1</t>
   </si>
   <si>
@@ -329,24 +263,6 @@
     <t>M45</t>
   </si>
   <si>
-    <t>M46</t>
-  </si>
-  <si>
-    <t>Nothing to Add</t>
-  </si>
-  <si>
-    <t>Nothing to Add to the Menu</t>
-  </si>
-  <si>
-    <t>M47</t>
-  </si>
-  <si>
-    <t>End</t>
-  </si>
-  <si>
-    <t>No Cat</t>
-  </si>
-  <si>
     <t>Breakfast</t>
   </si>
   <si>
@@ -408,6 +324,96 @@
   </si>
   <si>
     <t>Any Meal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מגוון חביתות, עשבי תיבול, בצל, פטריות </t>
+  </si>
+  <si>
+    <t>מגוון ירקות צלויים בתנור , ירקות זמינים בהתאם לעונה</t>
+  </si>
+  <si>
+    <t>ברוסקטות במגוון טעמים</t>
+  </si>
+  <si>
+    <t>פלטת גבינות קשות ורכות עם מתבלים שונים</t>
+  </si>
+  <si>
+    <t>טורטיות במגוון טעמים ומגוון מילויים</t>
+  </si>
+  <si>
+    <t>קישים \ פשטידות בטעמים של בטטה, פטריות, ברוקולי כרישה ועוד</t>
+  </si>
+  <si>
+    <t>חלה במילוי של מגוון גבינות עם פלפלים קלויים</t>
+  </si>
+  <si>
+    <t>פיצות במגוון טעמים כמו נפוליטנה, כמהין, זיתים, בצל ועוד</t>
+  </si>
+  <si>
+    <t>דגים מטוגנים בתוספת צ'יפס מטוגן</t>
+  </si>
+  <si>
+    <t>פסטה במגוון טעמים כמו רוזה, שמנת פטריות ועוד לפי בקשה מיוחדת</t>
+  </si>
+  <si>
+    <t>מגוון חסות, עלי בייבי, אגסים, אגס ביין, פקאן מסוכר וגבינת קממבר</t>
+  </si>
+  <si>
+    <t>מגוון חסות, עלי בייבי, גזר, מלפפון, עגבניות שרי, פלפל קלוי, זיתים וגבינה בולגרית</t>
+  </si>
+  <si>
+    <t>מגוון חסות, אנדיב, סלק, תפוז, אגוזי מלך, גבינת גאודה</t>
+  </si>
+  <si>
+    <t>מגוון חסות, גזר, עגבניות שרי, תפוח ירוק, עדשים וגרנולה</t>
+  </si>
+  <si>
+    <t>מגוון חסות, עלי בייבי, פלפל קלוי, עגבניות שרי וארטישוק</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מגוון קינוחים ובין היתר, עוגה בחושה, עוגת שמרים ועוגת גבינה </t>
+  </si>
+  <si>
+    <t>קפה חם או תה חם לפי בקשה</t>
+  </si>
+  <si>
+    <t>מיץ תפוזים טבעי סחוט</t>
+  </si>
+  <si>
+    <t>מיץ לימונדה בייצור עצמי</t>
+  </si>
+  <si>
+    <t>קציצות דגים ברוטב עגבניות בסגנון מרוקאי</t>
+  </si>
+  <si>
+    <t>דג סלומון אפוי בתנור ברוטב מרינדה</t>
+  </si>
+  <si>
+    <t>נבטי חמניה, עגבניות שרי, קונפי שום וזיתים</t>
+  </si>
+  <si>
+    <t>בירה מקומית מחבית</t>
+  </si>
+  <si>
+    <t>מגוון שתיה מוגזת</t>
+  </si>
+  <si>
+    <t>מגוון משקאות אלכוהולים כמו כוס יין, עראק, אוזו, ג'ין וכד'</t>
+  </si>
+  <si>
+    <t>פלטה של פירות העונה</t>
+  </si>
+  <si>
+    <t>נגיעות של פטיפורים, טריקולד, פאי לימון, טרמיסו, טארטים וכד'</t>
+  </si>
+  <si>
+    <t>Ravioli</t>
+  </si>
+  <si>
+    <t>רביולי תרד או ערמונים עם רטבים שונים לפי זמינות</t>
+  </si>
+  <si>
+    <t>Fish meatballs</t>
   </si>
 </sst>
 </file>
@@ -880,14 +886,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22F376A0-2B51-4EBE-9FE5-C2A407AB1D00}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.25" customWidth="1"/>
     <col min="2" max="2" width="31" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.9140625" customWidth="1"/>
     <col min="7" max="7" width="13.6640625" customWidth="1"/>
     <col min="8" max="8" width="12.4140625" customWidth="1"/>
@@ -895,45 +901,45 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F2">
         <v>120</v>
@@ -941,19 +947,19 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="F3">
         <v>120</v>
@@ -961,19 +967,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="F4">
         <v>120</v>
@@ -981,19 +987,19 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>120</v>
@@ -1001,19 +1007,19 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="F6">
         <v>120</v>
@@ -1021,19 +1027,19 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="F7">
         <v>120</v>
@@ -1041,19 +1047,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="F8">
         <v>120</v>
@@ -1061,19 +1067,19 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" t="s">
         <v>104</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
       </c>
       <c r="F9">
         <v>120</v>
@@ -1081,19 +1087,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="F10">
         <v>120</v>
@@ -1101,19 +1107,19 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="F11">
         <v>120</v>
@@ -1121,19 +1127,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="F12">
         <v>120</v>
@@ -1141,19 +1147,19 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" t="s">
         <v>108</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
       </c>
       <c r="F13">
         <v>120</v>
@@ -1161,19 +1167,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="F14">
         <v>120</v>
@@ -1181,19 +1187,19 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="F15">
         <v>120</v>
@@ -1201,19 +1207,19 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="F16">
         <v>120</v>
@@ -1221,19 +1227,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="F17">
         <v>120</v>
@@ -1241,19 +1247,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="F18">
         <v>120</v>
@@ -1261,19 +1267,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="F19">
         <v>120</v>
@@ -1281,19 +1287,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="F20">
         <v>120</v>
@@ -1301,19 +1307,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="F21">
         <v>160</v>
@@ -1321,19 +1327,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="F22">
         <v>160</v>
@@ -1341,19 +1347,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="F23">
         <v>160</v>
@@ -1361,19 +1367,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>160</v>
@@ -1381,19 +1387,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E25" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="F25">
         <v>160</v>
@@ -1401,19 +1407,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="F26">
         <v>160</v>
@@ -1421,19 +1427,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="F27">
         <v>160</v>
@@ -1441,19 +1447,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="F28">
         <v>160</v>
@@ -1461,19 +1467,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C29" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" t="s">
         <v>105</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
       </c>
       <c r="F29">
         <v>160</v>
@@ -1481,19 +1487,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="F30">
         <v>160</v>
@@ -1501,19 +1507,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="F31">
         <v>160</v>
@@ -1521,19 +1527,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B32" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="E32" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="F32">
         <v>160</v>
@@ -1541,19 +1547,19 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B33" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="E33" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="F33">
         <v>160</v>
@@ -1561,19 +1567,19 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="F34">
         <v>160</v>
@@ -1581,19 +1587,19 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="F35">
         <v>160</v>
@@ -1601,19 +1607,19 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="E36" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="F36">
         <v>160</v>
@@ -1621,19 +1627,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="E37" t="s">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="F37">
         <v>160</v>
@@ -1641,19 +1647,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="E38" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="F38">
         <v>160</v>
@@ -1661,19 +1667,19 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="E39" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="F39">
         <v>160</v>
@@ -1681,19 +1687,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="F40">
         <v>160</v>
@@ -1701,19 +1707,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C41" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E41" t="s">
         <v>115</v>
-      </c>
-      <c r="E41" t="s">
-        <v>36</v>
       </c>
       <c r="F41">
         <v>160</v>
@@ -1721,19 +1727,19 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E42" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="G42">
         <v>35</v>
@@ -1741,19 +1747,19 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="D43" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="G43">
         <v>6</v>
@@ -1761,19 +1767,19 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="G44">
         <v>45</v>
@@ -1781,19 +1787,19 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" t="s">
         <v>96</v>
       </c>
-      <c r="B45" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45" t="s">
-        <v>124</v>
-      </c>
       <c r="D45" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E45" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G45">
         <v>10</v>
@@ -1801,65 +1807,28 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="D46" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E46" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="G46">
         <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>98</v>
-      </c>
-      <c r="B47" t="s">
-        <v>99</v>
-      </c>
-      <c r="C47" t="s">
-        <v>124</v>
-      </c>
-      <c r="D47" t="s">
-        <v>103</v>
-      </c>
-      <c r="E47" t="s">
-        <v>100</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>101</v>
-      </c>
-      <c r="B48" t="s">
-        <v>102</v>
-      </c>
-      <c r="D48" t="s">
-        <v>102</v>
-      </c>
-      <c r="E48" t="s">
-        <v>102</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="44" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="44" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
